--- a/data/trans_orig/P04C05_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P04C05_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con refrigeración por aire acondicionado mediante aparatos fijos en la vivienda en 2023</t>
+          <t>Población según si dispone de refrigeración por aire acondicionado mediante aparatos fijos en la vivienda en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73658</t>
+          <t>74297</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111266</t>
+          <t>111920</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85272</t>
+          <t>84327</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115964</t>
+          <t>114044</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>165915</t>
+          <t>164755</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>215724</t>
+          <t>217705</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13215</t>
+          <t>12374</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9682</t>
+          <t>9466</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17219</t>
+          <t>17218</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>389144</t>
+          <t>388866</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>428354</t>
+          <t>427170</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>325264</t>
+          <t>326391</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>356247</t>
+          <t>356805</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>727529</t>
+          <t>725807</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>776799</t>
+          <t>776911</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,67%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63398</t>
+          <t>64022</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97967</t>
+          <t>97869</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73726</t>
+          <t>73094</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100965</t>
+          <t>102865</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>143499</t>
+          <t>145314</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>191071</t>
+          <t>191663</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15458</t>
+          <t>14914</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,82 +1314,82 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2931</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>7236</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>9358</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>4478</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>17608</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>0,54%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>2931</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>6897</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>9358</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>4717</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>18245</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>347243</t>
+          <t>346683</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>381251</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>278324</t>
+          <t>276618</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>306159</t>
+          <t>306540</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>633779</t>
+          <t>634935</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>682463</t>
+          <t>680807</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,55%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32064</t>
+          <t>37395</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>157057</t>
+          <t>159343</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29133</t>
+          <t>29417</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46121</t>
+          <t>46007</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>56403</t>
+          <t>52891</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>197194</t>
+          <t>194291</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1607</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15048</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15072</t>
+          <t>15043</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>498882</t>
+          <t>496259</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>633186</t>
+          <t>625968</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119306</t>
+          <t>119448</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>136421</t>
+          <t>136110</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>625709</t>
+          <t>627942</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>773676</t>
+          <t>778138</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>229833</t>
+          <t>230665</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>292461</t>
+          <t>290173</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>124447</t>
+          <t>106225</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>290380</t>
+          <t>288095</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>340212</t>
+          <t>331933</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>547819</t>
+          <t>549346</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,34%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20257</t>
+          <t>21409</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12708</t>
+          <t>12642</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11766</t>
+          <t>12589</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28723</t>
+          <t>31298</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>729861</t>
+          <t>732362</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>793033</t>
+          <t>791946</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>676941</t>
+          <t>679146</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>846602</t>
+          <t>866968</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1441915</t>
+          <t>1440016</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1661716</t>
+          <t>1666733</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,94%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>147282</t>
+          <t>145959</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>191585</t>
+          <t>190746</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>221165</t>
+          <t>216348</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>444662</t>
+          <t>435463</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>384494</t>
+          <t>384317</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>593696</t>
+          <t>593509</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,13%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11058</t>
+          <t>11484</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16354</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>9788</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22966</t>
+          <t>22992</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>278319</t>
+          <t>279661</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>322294</t>
+          <t>323835</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>388682</t>
+          <t>398851</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>607234</t>
+          <t>613940</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>708648</t>
+          <t>704968</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>916349</t>
+          <t>914029</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,5%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>37797</t>
+          <t>38567</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>82875</t>
+          <t>85538</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>194078</t>
+          <t>193808</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>241308</t>
+          <t>243458</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>246058</t>
+          <t>242919</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>311557</t>
+          <t>306968</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>946</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8250</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2333</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7974</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>157253</t>
+          <t>154848</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>202406</t>
+          <t>201901</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>516472</t>
+          <t>513038</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>564257</t>
+          <t>563388</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>684997</t>
+          <t>689677</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>751222</t>
+          <t>754096</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,27%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>567546</t>
+          <t>578769</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>828894</t>
+          <t>836234</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>795202</t>
+          <t>798289</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1099104</t>
+          <t>1078287</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1476038</t>
+          <t>1460791</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1868844</t>
+          <t>1855260</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24525</t>
+          <t>23851</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49767</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22183</t>
+          <t>23002</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>40645</t>
+          <t>40513</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>51494</t>
+          <t>50236</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>83851</t>
+          <t>81825</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2507882</t>
+          <t>2500497</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2781640</t>
+          <t>2767351</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2442862</t>
+          <t>2470385</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2749313</t>
+          <t>2753228</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5013604</t>
+          <t>5024871</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5418832</t>
+          <t>5433517</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04C05_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P04C05_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>91240</t>
+          <t>104864</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74297</t>
+          <t>86273</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111920</t>
+          <t>126156</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>98382</t>
+          <t>109526</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>84327</t>
+          <t>93474</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114044</t>
+          <t>125355</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>189621</t>
+          <t>214390</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>164755</t>
+          <t>191636</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>217705</t>
+          <t>241118</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12374</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>15911</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>11862</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17218</t>
+          <t>22792</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>409771</t>
+          <t>441353</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>388866</t>
+          <t>419414</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>427170</t>
+          <t>460099</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>342707</t>
+          <t>369992</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>326391</t>
+          <t>353564</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>356805</t>
+          <t>386933</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>752477</t>
+          <t>811345</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>725807</t>
+          <t>785711</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>776911</t>
+          <t>835992</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>80,57%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>446125</t>
+          <t>486979</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>446125</t>
+          <t>486979</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>446125</t>
+          <t>486979</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>951337</t>
+          <t>1037597</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>951337</t>
+          <t>1037597</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>951337</t>
+          <t>1037597</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>78751</t>
+          <t>84231</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64022</t>
+          <t>67134</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97869</t>
+          <t>102588</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>87414</t>
+          <t>98594</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73094</t>
+          <t>83924</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>102865</t>
+          <t>117328</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>166165</t>
+          <t>182825</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>145314</t>
+          <t>157888</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>191663</t>
+          <t>207820</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>8010</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>16591</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>946</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>9358</t>
+          <t>11165</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4478</t>
+          <t>5758</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17608</t>
+          <t>20727</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>367035</t>
+          <t>390971</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>346683</t>
+          <t>371967</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>381251</t>
+          <t>408688</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>292235</t>
+          <t>321394</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>276618</t>
+          <t>301613</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>306540</t>
+          <t>335045</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>659270</t>
+          <t>712365</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>634935</t>
+          <t>686349</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>680807</t>
+          <t>735741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>95085</t>
+          <t>106453</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37395</t>
+          <t>88920</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>159343</t>
+          <t>126020</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37220</t>
+          <t>41251</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29417</t>
+          <t>32825</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46007</t>
+          <t>52194</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>132305</t>
+          <t>147705</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>52891</t>
+          <t>124072</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>194291</t>
+          <t>169577</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>25,79%</t>
         </is>
       </c>
     </row>
@@ -1750,69 +1750,69 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1607</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15244</t>
+          <t>13830</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4260</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
           <t>2,28%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3015</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>11</t>
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>8705</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15043</t>
+          <t>15890</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>565064</t>
+          <t>356790</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>496259</t>
+          <t>336803</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>625968</t>
+          <t>374954</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>128344</t>
+          <t>144268</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119448</t>
+          <t>133813</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>136110</t>
+          <t>152568</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>693408</t>
+          <t>501058</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>627942</t>
+          <t>478815</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>778138</t>
+          <t>524914</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>79,84%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>667290</t>
+          <t>470669</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>667290</t>
+          <t>470669</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>667290</t>
+          <t>470669</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166254</t>
+          <t>186799</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166254</t>
+          <t>186799</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166254</t>
+          <t>186799</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>833544</t>
+          <t>657468</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>833544</t>
+          <t>657468</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>833544</t>
+          <t>657468</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>258579</t>
+          <t>298343</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>230665</t>
+          <t>267609</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>290173</t>
+          <t>330768</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>221670</t>
+          <t>253582</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>106225</t>
+          <t>232372</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>288095</t>
+          <t>279643</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>480249</t>
+          <t>551925</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>331933</t>
+          <t>512191</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>549346</t>
+          <t>592653</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12064</t>
+          <t>14915</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21409</t>
+          <t>24887</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>10152</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12642</t>
+          <t>17134</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>19355</t>
+          <t>25067</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12589</t>
+          <t>16797</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31298</t>
+          <t>37072</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>763156</t>
+          <t>817499</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>732362</t>
+          <t>784337</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>791946</t>
+          <t>847722</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>746854</t>
+          <t>594312</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>679146</t>
+          <t>568557</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>866968</t>
+          <t>617721</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1510010</t>
+          <t>1411812</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1440016</t>
+          <t>1371180</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1666733</t>
+          <t>1451926</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>73,01%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1033799</t>
+          <t>1130757</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1033799</t>
+          <t>1130757</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1033799</t>
+          <t>1130757</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>975815</t>
+          <t>858046</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>975815</t>
+          <t>858046</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>975815</t>
+          <t>858046</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2009614</t>
+          <t>1988804</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2009614</t>
+          <t>1988804</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2009614</t>
+          <t>1988804</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>168109</t>
+          <t>227632</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>145959</t>
+          <t>202345</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>190746</t>
+          <t>252627</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>278149</t>
+          <t>240803</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>216348</t>
+          <t>219440</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>435463</t>
+          <t>262893</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>446257</t>
+          <t>468434</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>384317</t>
+          <t>435924</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>593509</t>
+          <t>505688</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>11025</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11484</t>
+          <t>20047</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>11569</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6982</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>18304</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>15420</t>
+          <t>22595</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9788</t>
+          <t>15223</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22992</t>
+          <t>31526</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>301615</t>
+          <t>329307</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>279661</t>
+          <t>303923</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>323835</t>
+          <t>354144</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>551838</t>
+          <t>577080</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>398851</t>
+          <t>553486</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>613940</t>
+          <t>598219</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>853453</t>
+          <t>906387</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>704968</t>
+          <t>869815</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>914029</t>
+          <t>937743</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>67,11%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>840084</t>
+          <t>829453</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>840084</t>
+          <t>829453</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>840084</t>
+          <t>829453</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1315130</t>
+          <t>1397416</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1315130</t>
+          <t>1397416</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1315130</t>
+          <t>1397416</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2990,7 +2990,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>58835</t>
+          <t>52699</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>38567</t>
+          <t>34496</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>85538</t>
+          <t>76510</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>216033</t>
+          <t>240802</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>193808</t>
+          <t>215025</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>243458</t>
+          <t>268026</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>274868</t>
+          <t>293501</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>242919</t>
+          <t>265048</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>306968</t>
+          <t>332519</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,75%</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>9656</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7699</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>6907</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2402</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8395</t>
+          <t>13865</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>181510</t>
+          <t>182707</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>154848</t>
+          <t>159610</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>201901</t>
+          <t>200656</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>540995</t>
+          <t>598393</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>513038</t>
+          <t>571642</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>563388</t>
+          <t>625129</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>722505</t>
+          <t>781101</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>689677</t>
+          <t>742195</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>754096</t>
+          <t>810462</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>74,94%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>750599</t>
+          <t>874222</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>578769</t>
+          <t>817010</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>836234</t>
+          <t>939402</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>938867</t>
+          <t>984559</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>798289</t>
+          <t>936510</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1078287</t>
+          <t>1035641</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1689466</t>
+          <t>1858780</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1460791</t>
+          <t>1781209</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1855260</t>
+          <t>1935954</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>35317</t>
+          <t>47599</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23851</t>
+          <t>35134</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49767</t>
+          <t>64258</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>30389</t>
+          <t>38703</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23002</t>
+          <t>30165</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>40513</t>
+          <t>52412</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>65707</t>
+          <t>86301</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>50236</t>
+          <t>69152</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>81825</t>
+          <t>105894</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2588151</t>
+          <t>2518628</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2500497</t>
+          <t>2453445</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2767351</t>
+          <t>2576035</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2602973</t>
+          <t>2605440</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2470385</t>
+          <t>2551546</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2753228</t>
+          <t>2651711</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>5191124</t>
+          <t>5124066</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5024871</t>
+          <t>5043799</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5433517</t>
+          <t>5206186</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>73,65%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3374067</t>
+          <t>3440448</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3374067</t>
+          <t>3440448</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3374067</t>
+          <t>3440448</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3572229</t>
+          <t>3628701</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3572229</t>
+          <t>3628701</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3572229</t>
+          <t>3628701</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6946296</t>
+          <t>7069148</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6946296</t>
+          <t>7069148</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6946296</t>
+          <t>7069148</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
